--- a/data/trans_orig/IP31C_R_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31C_R_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6725</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3039</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12909</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,52%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5480</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2428</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10670</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13067</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12144</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20352</t>
+          <t>20497</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46990</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>40806</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50676</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,48%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>48219</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43029</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>51271</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>89,79%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>80,13%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,48%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51681</t>
+          <t>39938</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45278</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55223</t>
+          <t>43283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>99899</t>
+          <t>86928</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>91691</t>
+          <t>79123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104312</t>
+          <t>92300</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,107 +1063,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25430</t>
+          <t>39791</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>28606</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35583</t>
+          <t>50809</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33550</t>
+          <t>33864</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24846</t>
+          <t>24723</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44979</t>
+          <t>47761</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>92</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>58980</t>
+          <t>73654</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45172</t>
+          <t>59319</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73987</t>
+          <t>91207</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -1176,107 +1176,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>575</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>424668</t>
+          <t>424880</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414515</t>
+          <t>413862</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>432846</t>
+          <t>436065</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>582</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>469777</t>
+          <t>389251</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>458348</t>
+          <t>375354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>478481</t>
+          <t>398392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>894445</t>
+          <t>814133</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>879438</t>
+          <t>796580</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>908253</t>
+          <t>828468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>464671</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>464671</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>464671</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>622</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>450098</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>450098</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>450098</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>503327</t>
+          <t>423115</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>503327</t>
+          <t>423115</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>503327</t>
+          <t>423115</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>953425</t>
+          <t>887787</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>953425</t>
+          <t>887787</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>953425</t>
+          <t>887787</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,107 +1406,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>26801</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25546</t>
+          <t>36656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25049</t>
+          <t>19697</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>13443</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35810</t>
+          <t>27470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>42179</t>
+          <t>46498</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31445</t>
+          <t>36519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53129</t>
+          <t>58813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -1519,107 +1519,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>198</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>128670</t>
+          <t>139885</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120254</t>
+          <t>130030</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134367</t>
+          <t>146907</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>196</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>156090</t>
+          <t>127099</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145329</t>
+          <t>119326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163266</t>
+          <t>133353</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>394</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>284760</t>
+          <t>266983</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>273810</t>
+          <t>254668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295494</t>
+          <t>276962</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>145800</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>145800</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>145800</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>146796</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>146796</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>146796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>326939</t>
+          <t>313481</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>326939</t>
+          <t>313481</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>326939</t>
+          <t>313481</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,107 +1749,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48040</t>
+          <t>73317</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35780</t>
+          <t>60289</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61210</t>
+          <t>90234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52179</t>
+          <t>45924</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80544</t>
+          <t>73682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>167</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>113304</t>
+          <t>132844</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94565</t>
+          <t>113590</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134264</t>
+          <t>155748</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -1862,107 +1862,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>842</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>601557</t>
+          <t>611755</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>588387</t>
+          <t>594838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613817</t>
+          <t>624783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>838</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>677547</t>
+          <t>556288</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>662267</t>
+          <t>542134</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>690632</t>
+          <t>569892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1279104</t>
+          <t>1168044</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1258144</t>
+          <t>1145140</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1297843</t>
+          <t>1187298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>910</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>649597</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>649597</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>649597</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>615816</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>615816</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>615816</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1392408</t>
+          <t>1300888</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1392408</t>
+          <t>1300888</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1392408</t>
+          <t>1300888</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
